--- a/docs/parts_review.xlsx
+++ b/docs/parts_review.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Needs Clarification" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Needs Review'!$A$1:$I$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Needs Review'!$A$1:$J$72</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Needs Clarification'!$A$1:$I$275</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -449,10 +449,11 @@
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -483,20 +484,25 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Part Page</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Quick Search</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Correct Product / Model (fill in)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Correct URL (fill in)</t>
         </is>
@@ -526,16 +532,23 @@
           <t>Generic commodity item sold under many brand names on Amazon/eBay/AliExpress with no single canonical manufacturer; linked to a well-documented vendor reference page rather than one storefront listing.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>#38/Drawer 3</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -561,16 +574,23 @@
           <t>Sold under many brand names as near-identical clones; Adafruit's version (PID 618) is the most thoroughly documented reference and is used here as the representative link, though the exact board on hand may be an unbranded clone.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>#40/Drawer 20</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -596,16 +616,23 @@
           <t>Generic commodity relay module with no single canonical manufacturer; nearly identical boards are sold under many brand names (Keyestudio, SainSmart, generic AliExpress/eBay listings).</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>#38/Drawer 1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -631,16 +658,23 @@
           <t>Generic commodity item sold under many brand names (SainSmart, Keyestudio, SunFounder, etc.) with no single canonical manufacturer; the SainSmart listing (now discontinued) is used as a representative reference.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>#39/Drawer 10</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -666,16 +700,23 @@
           <t>Generic commodity item widely sold under many brand names (SainSmart, JBtek, generic AliExpress/eBay listings) with no single canonical manufacturer.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>#38/Drawer 6</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -701,16 +742,23 @@
           <t>Sold under many brand names (SparkFun, Adafruit "FTDI Friend", generic clones) with no single canonical manufacturer; SparkFun's well-documented version is used here as the representative reference.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>#38/Drawer 6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -736,16 +784,23 @@
           <t>The label is generic - Adafruit has sold many distinct 'Bluefruit' products over the years (UART Friend v2 #2479, this SPI/UART Friend v3.0 #2267, SPI Friend #2633, Feather 32u4 Bluefruit LE, Feather nRF52832, Bluefruit LE Sniffer, EZ-Link, etc). Matched to the standalone 'Bluefruit LE Friend' breakout since the inventory calls it a 'board' rather than a 'feather' or 'shield'. The learn guide has no separate Pinouts sub-page (fetch returned 404), and Adafruit's own downloads page links only to Nordic's nRF51822 product page, not a direct PDF, so datasheet_url is left null.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>#38/Drawer 3</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -771,16 +826,23 @@
           <t>Adafruit sold this as both a breakout (with onboard ceramic antenna, product 1469, or with a uFL connector for external antenna, product 1510) and as an Arduino shield - the generic label doesn't distinguish. Picked the onboard-antenna breakout as the most common variant. Product is discontinued/out of stock; the learn guide is an older single/multi-page format with no distinct Pinouts sub-page, and no direct chip datasheet PDF is linked from Adafruit's own pages (they link out to TI's product page instead).</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>#38/Drawer 3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -806,18 +868,23 @@
           <t>Deliberately not matched to a specific SKU per instructions - Adafruit sells dozens of distinct 'Feather' boards and the inventory label gives no way to tell which chip/variant this is. Linked to the Feather family overview/introduction guide instead of guessing a specific product.</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>#38/Drawer 6; #39/Drawer 11; #39/Drawer 11</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -843,16 +910,23 @@
           <t>Label 'feather s3 board' is generic among several ESP32-S3 Feather SKUs Adafruit sells (plain #5477/#5323, ESP32-S3 TFT Feather #5483, ESP32-S3 Reverse TFT Feather #5691, w.FL antenna version #5885, plus the third-party 'FeatherS3' by Unexpected Maker #5399). Picked the plain STEMMA QT ESP32-S3 Feather (4MB/2MB PSRAM) as the most 'default' interpretation, but this is a guess.</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>#39/Drawer 11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -878,16 +952,23 @@
           <t>Adafruit sells this as a bare-bones PCB-only version (#5100), a Starter Kit with switches/keycaps/enclosure (#5128, part of ADABOX019), and a separate enclosure/hardware add-on pack (#5103). Linked to the Starter Kit as the most complete/common variant; the physical inventory item could be any of these.</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>#62</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -913,14 +994,24 @@
           <t>Distinct from Metro Mini (id 471) per instructions. 'Metro' could also refer to the Metro M0 Express or Metro M4 Express (different, faster SAMD chips) - picked the original ATmega328-based Metro as the default/classic 'Metro'. There isn't a dedicated Learn System guide page for this exact board (only project guides like 'Experimenter's Guide for Metro' and the general 'How to Choose a Microcontroller' reference it), so learn_guide_url and pinout_image_url are left null; no direct chip datasheet PDF is linked from Adafruit's own pages either (they link to Microchip/Atmel's product page).</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>#40/Drawer 21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://www.adafruit.com/product/2488</t>
         </is>
       </c>
     </row>
@@ -948,14 +1039,24 @@
           <t>The original (V1, CP2104-based, no STEMMA QT) Metro Mini has been superseded by this V2; if the physical part predates ~2022 it may actually be the older V1 board, which looks nearly identical but lacks the STEMMA QT connector. No direct chip datasheet PDF is linked from Adafruit's own pages.</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>#38/Drawer 4</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://www.adafruit.com/product/2590</t>
         </is>
       </c>
     </row>
@@ -983,14 +1084,24 @@
           <t>Per hint, matched to the Mini PiTFT family. Adafruit's Mini PiTFT guide covers two closely related products sharing the same connector/pinout: the 1.3" 240x240 (#4484, matched here) and the 1.14" 240x135 (#4302) - the generic 'minipitft' label can't distinguish which one is actually in the drawer.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>#40/Drawer 21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://www.adafruit.com/product/4484</t>
         </is>
       </c>
     </row>
@@ -1018,18 +1129,23 @@
           <t>Per the hint, "adfruit" is a typo of "adafruit." Too generic to guess a specific chip variant with confidence, so linked to Adafruit's own Feather family overview instead of a specific product SKU.</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>#39/Drawer 10; #39/Drawer 11</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1055,18 +1171,23 @@
           <t>"Amiga keyboard" doesn't specify which Amiga model it came from (each uses a different keyboard/membrane design), so no single specific product page applies; image_url is a Wikimedia Commons page showing an A500 system including its keyboard, not a bare direct image file link.</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>#66</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1092,18 +1213,23 @@
           <t>No identifying details given; too vague to match a specific product. Linked to Arduino's own homepage rather than guessing a specific board.</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>#40/Drawer 21</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1129,18 +1255,23 @@
           <t>Per the hint, this is a vague catch-all description covering multiple unspecified items, not a single identifiable product - deliberately left unmatched rather than fabricating a specific board.</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>#75</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1166,18 +1297,23 @@
           <t>Same ambiguity as item 293 ("arduino"); no identifying details given, so left generic rather than guessing a specific board.</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>#40/Drawer 19; #62</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1203,18 +1339,23 @@
           <t>Plural version of items 293/555; still no identifying details given, so left generic rather than guessing specific boards.</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>#40/Drawer 19</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1240,18 +1381,23 @@
           <t>By definition these are unbranded/non-canonical products (that is what makes them "clones"); no single manufacturer, specific model, or product page applies.</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>#38/Drawer 6</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="n"/>
-      <c r="I22" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1277,14 +1423,24 @@
           <t>Item is labeled "arduino" but "HAT" is Raspberry-Pi-specific terminology - likely a labeling mix-up by the cataloger, or they may have meant Adafruit's similarly-named Motor/Stepper Shield for Arduino (adafruit.com/product/1438). Flagging this ambiguity rather than picking one silently.</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>#38/Drawer 3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://www.adafruit.com/product/2348</t>
         </is>
       </c>
     </row>
@@ -1312,18 +1468,23 @@
           <t>Ambiguous: could be Arduino's own official (now-retired) WiFi Shield (arduino.cc/en/Main/ArduinoWiFiShield, based on the HDG204 module), or - more likely given hobbyist prevalence - a generic ESP8266/ESP-01 WiFi module/shield. Left low confidence given this ambiguity; distinct from item 405 (ESP32 dev board) and 479 (ESP-12E dev board), which are standalone boards rather than "modules."</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>#38/Drawer 1</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr"/>
+      <c r="J24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1349,16 +1510,23 @@
           <t>The original creator (Digistump) is defunct; boards sold today are third-party clones/continuations of the open-source Digispark design, so no single current canonical manufacturer exists. "ATtiny85 board" could in principle refer to a different, non-Digispark ATtiny85 breakout, but Digispark is by far the most common.</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>#38/Drawer 6</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1384,18 +1552,23 @@
           <t>Name is a probable mangled typo of "BLEduino" per the hint. Could alternatively be a generic BLE/Bluetooth shield (e.g. Adafruit Bluefruit LE Shield, RedBearLab BLE Shield). Low confidence because BLEduino was a small 2013 Kickstarter product that is long discontinued with limited surviving official documentation, so the exact match can't be fully confirmed from the label alone.</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>#38/Drawer 9; #38/Drawer 9</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="n"/>
-      <c r="I26" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -1421,18 +1594,23 @@
           <t>Too generic to identify a specific brand/product - could be any of many near-identical HC-05/HC-06 shields, or a BLE shield such as Adafruit's Bluefruit LE. Treated as a separate, unrelated entry from item 258 ("bleduinio shield").</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>#38/Drawer 9</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="n"/>
-      <c r="I27" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
+      <c r="J27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -1458,18 +1636,23 @@
           <t>Per the hint, this is a literal internal metal shielding part, not a purchasable electronic "product" with a canonical manufacturer or model number - described generically with a reference article in place of a storefront link.</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>#66</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1495,16 +1678,23 @@
           <t>Generic/commodity dev board manufactured and sold by many vendors under the community "NodeMCU" open-source design, with no single canonical manufacturer; components101 used as a well-documented reference rather than one storefront listing.</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>#38/Drawer 4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1530,16 +1720,23 @@
           <t>Commodity item sold under many brand names/unbranded clones with no single canonical manufacturer; linked to a well-documented reference/pinout page instead of a single storefront listing.</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>#38/Drawer 6</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1565,14 +1762,24 @@
           <t>Product ID #1260 is the same physical listing across revisions; hand-written label says 'v2' but current page describes v3 (SK6812 chip) -- datasheet omitted rather than risk citing the wrong chip.</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>#38/Drawer 5</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://thepihut.com/products/adafruit-flora-rgb-smart-neopixel-version-2-pack-of-4</t>
         </is>
       </c>
     </row>
@@ -1600,16 +1807,23 @@
           <t>Brand unambiguous, exact model unknown. Linked to Fluke's multimeter category page.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>#60</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -1635,18 +1849,23 @@
           <t>No specific module indicated by name.</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>#38/Drawer 1</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -1672,18 +1891,23 @@
           <t>Used Adafruit's HDMI Plug Breakout Board (3119) as representative example only.</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>#39/Drawer 13</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -1709,18 +1933,23 @@
           <t>No brand/model given; BTS7960-based modules used as representative reference.</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>#60</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="n"/>
-      <c r="I35" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -1746,18 +1975,23 @@
           <t>Hand-written label gives no LED count or RGB/RGBW variant, so no single specific product can be confidently matched.</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>#39/Drawer 10</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1783,16 +2017,23 @@
           <t>Could be a genuine Saleae unit, but generic FX2 clone is far more common in hobbyist workshops.</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>#52</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1818,16 +2059,23 @@
           <t>Verified as a real, specific Adafruit product (#1768), 1/4 of the 60-LED ring (15 LEDs per piece).</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>#38/Drawer 5</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -1853,18 +2101,23 @@
           <t>Same ambiguity as item 64 -- no LED count specified, treated as a generic/family match.</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>#38/Drawer 5</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="n"/>
-      <c r="I39" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -1890,18 +2143,23 @@
           <t>Essentially unidentifiable beyond general category.</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>#39/Drawer 14</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1927,16 +2185,23 @@
           <t>Could be Zero, Zero W, or Zero 2 W; picked original as base/iconic match.</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>#39/Drawer 11</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -1962,18 +2227,23 @@
           <t>Plural, no brand specified; could be third-party equivalents.</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>#39/Drawer 11</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -1999,18 +2269,23 @@
           <t>No specific expansion board named; hundreds of official/third-party HATs exist.</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>#39/Drawer 11</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
@@ -2036,18 +2311,23 @@
           <t>Extremely generic plural label with no model info.</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>#41</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
@@ -2073,18 +2353,23 @@
           <t>No specific product named; Adafruit Pi T-Cobbler Plus linked as representative example. Plural 'boards' may mean multiple items.</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>#38/Drawer 4</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="n"/>
-      <c r="I45" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2110,16 +2395,23 @@
           <t>Label only says 'raspi camera' with no version given; Camera Module 2 (IMX219) picked as the representative match.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>#39/Drawer 10</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2145,16 +2437,23 @@
           <t>No single specific cable identifiable; used official RPi Foundation 'Camera Cable' product as representative.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>#38/Drawer 4; #41</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -2180,18 +2479,23 @@
           <t>No official RPi camera case exists; Adafruit product 3253 used as representative example only.</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>#39/Drawer 11</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="n"/>
-      <c r="I48" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -2217,18 +2521,23 @@
           <t>Label likely a typo for 'lens'. No canonical single product — generic commodity category.</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>#40/Drawer 26</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -2254,18 +2563,23 @@
           <t>No model/brand specified; possibly a near-duplicate of item 154.</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>#39/Drawer 14</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="n"/>
-      <c r="I50" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2291,16 +2605,23 @@
           <t>Real historic product from ~2012, long out of production; no live official product page found, linked RPi Forums thread instead.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>#41</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -2326,18 +2647,23 @@
           <t>Likely describes physical state rather than a distinct product; possibly duplicate of item 155.</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>#39/Drawer 14</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2363,16 +2689,23 @@
           <t>Similar kits also sold by Waveshare and others; exact kit owned not confirmable.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>#41</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -2398,18 +2731,23 @@
           <t>Not a product with a canonical manufacturer page; pinout.xyz linked as the closest real equivalent.</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>#39/Drawer 14</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2435,16 +2773,23 @@
           <t>Raspberry Pi sells several official supplies of different wattage (15W for Pi 4/400, 27W for Pi 5, older 12.5W micro-USB for earlier boards); which exact one was on hand is not specified, so this is a best-guess representative match rather than a confirmed SKU.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>#39/Drawer 14</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2470,16 +2815,23 @@
           <t>Label just says 'raspi zero' with no W/2W qualifier; could be the plain Pi Zero, Zero W, or newer Zero 2 W. Picked Zero W as the most commonly encountered variant in hobbyist stock.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>#40/Drawer 21</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2505,16 +2857,23 @@
           <t>This is a well-defined commodity product category (8-channel opto-isolated relay board) sold nearly identically under dozens of brand names; no single canonical manufacturer.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>#39/Drawer 11</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
@@ -2540,18 +2899,23 @@
           <t>Label gives no channel count or brand, and overlaps with separately-listed items 40 (8ch), 324 (single), and 352 (small) relay boards in this same inventory, so it's ambiguous which physical board this entry refers to.</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>#38/Drawer 3</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="n"/>
-      <c r="I58" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr"/>
+      <c r="J58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2577,16 +2941,23 @@
           <t>Picked as the most well-documented specific 'RFID reader breakout board,' but other common breakouts (e.g. MFRC522-based modules) are equally plausible matches for a generic label like this, so exact identity is not certain.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>#38/Drawer 6</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -2612,18 +2983,23 @@
           <t>'Robot motor driver' is too generic to pin down a single product; picked TB6612FNG as a widely used representative example, but L298N-based boards and others are equally common in hobby robotics.</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>#60</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2649,16 +3025,23 @@
           <t>Adafruit's version is the best-documented match for a generic 'servo controller board,' but unbranded PCA9685 clone boards (very common on Amazon/eBay) are visually near-identical and equally plausible.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>#38/Drawer 9</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2684,16 +3067,23 @@
           <t>Well-defined commodity category (single-channel 5V relay board); no single canonical manufacturer, virtually identical boards are sold under many brand names.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>#38/Drawer 3</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -2719,18 +3109,23 @@
           <t>Label is a vague plural ('small motor drivers') with no distinguishing detail, so no single product can be responsibly matched.</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>#60</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="n"/>
-      <c r="I63" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2756,16 +3151,23 @@
           <t>Adafruit also sells a smaller 12-LED ring (1.5in diameter, product #1643); 'small' is relative, so it could be either the 12- or 16-LED variant.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>#38/Drawer 5</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
@@ -2791,18 +3193,23 @@
           <t>Overlaps heavily with items 324 (single relay board) and 329 (relay module) in this inventory; likely the same generic type of part recorded under a slightly different label, so treated as low confidence for uniquely distinguishing which physical unit this is.</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>#38/Drawer 3</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="n"/>
-      <c r="I65" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
@@ -2828,18 +3235,23 @@
           <t>Sonos sells official wall mounts for specific speaker models, and third parties (Flexson, SANUS, Mount-It!) sell compatible brackets too; with no speaker model specified in the label, it's not possible to identify one specific mount.</t>
         </is>
       </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>#87</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="n"/>
-      <c r="I66" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
@@ -2865,18 +3277,23 @@
           <t>No size or spec given in the label, and this is a separate inventory entry from item 822 ('stepper motor nema 17'), so it's likely a different motor whose exact type cannot be determined.</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>#60</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="n"/>
-      <c r="I67" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
@@ -2902,18 +3319,23 @@
           <t>This is an accessory/mounting hardware item, not a specific electronic product; sold under many brands (StepperOnline, Weideer, generic Amazon listings) and also widely available as a 3D-printable design, so no single canonical product applies.</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>#39/Drawer 14</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="n"/>
-      <c r="I68" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2939,16 +3361,23 @@
           <t>Per the hint, treated as a standard motor size/type rather than a single manufacturer SKU; StepperOnline is one of the most common suppliers of this exact form factor, used here only as a representative reference.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>#51; #51; #51; #55</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
@@ -2974,18 +3403,23 @@
           <t>No single canonical manufacturer; Deftaudio (Tindie) and ProtoSupplies both sell small-batch Teensy MIDI DIN breakout boards, and many hobbyists also build one-off DIY versions from the classic MIDI optoisolator circuit, so the exact physical item can't be pinned down.</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>#38/Drawer 9</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="n"/>
-      <c r="I70" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr"/>
+      <c r="J70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
@@ -3011,18 +3445,23 @@
           <t>Label is a vague plural ('tft displays') with no size, resolution, or interface given; used Adafruit's well-documented 1.8in ST7735R display purely as a representative example of the category, not as a confirmed match.</t>
         </is>
       </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>#38/Drawer 9</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="n"/>
-      <c r="I71" s="3" t="n"/>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3048,162 +3487,169 @@
           <t>The original design and library are from Circuits@Home; the board itself is now sold by many vendors as a near-identical clone, so there is no single current canonical manufacturer page (circuitsathome.com's own store page returned a server error when checked).</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Open in app</t>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>#38/Drawer 1</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Google it</t>
-        </is>
-      </c>
+          <t>Open in app</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Google it</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I72"/>
+  <autoFilter ref="A1:J72"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId142"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3304,6 +3750,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3319,7 +3767,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>drawer a1</t>
+          <t>Drawer 1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3337,6 +3785,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3352,7 +3802,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>drawer a1</t>
+          <t>Drawer 1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3370,6 +3820,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3385,7 +3837,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>drawer a1</t>
+          <t>Drawer 1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3403,6 +3855,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3418,7 +3872,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>drawer a1</t>
+          <t>Drawer 1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3436,6 +3890,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3451,7 +3907,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>drawer a1</t>
+          <t>Drawer 1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3469,6 +3925,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3484,7 +3942,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>drawer a1</t>
+          <t>Drawer 1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3502,6 +3960,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3517,7 +3977,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>drawer a1</t>
+          <t>Drawer 1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3535,6 +3995,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3550,7 +4012,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>drawer a1</t>
+          <t>Drawer 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3568,6 +4030,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3583,7 +4047,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>drawer a1</t>
+          <t>Drawer 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -3601,6 +4065,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3616,7 +4082,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>drawer a1</t>
+          <t>Drawer 1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3632,6 +4098,11 @@
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Google it</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://www.electrokit.com/en/pyxy-synapse-sm700-wireless-dev-board</t>
         </is>
       </c>
     </row>
@@ -3649,7 +4120,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>drawer a1</t>
+          <t>Drawer 1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3667,6 +4138,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3682,7 +4155,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>drawer a1</t>
+          <t>Drawer 1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3700,6 +4173,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3715,7 +4190,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>drawer a2</t>
+          <t>Drawer 2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3733,6 +4208,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -3748,7 +4225,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>drawer a3</t>
+          <t>Drawer 3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3766,6 +4243,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3781,7 +4260,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>drawer a3</t>
+          <t>Drawer 3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3797,6 +4276,11 @@
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Google it</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://www.sparkfun.com/easydriver-stepper-motor-driver.html</t>
         </is>
       </c>
     </row>
@@ -3814,7 +4298,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>drawer b3</t>
+          <t>Drawer 12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3830,6 +4314,11 @@
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Google it</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>https://www.sparkfun.com/easydriver-stepper-motor-driver.html</t>
         </is>
       </c>
     </row>
@@ -3847,7 +4336,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>drawer a3</t>
+          <t>Drawer 3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3865,6 +4354,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3880,7 +4371,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3898,6 +4389,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3913,7 +4406,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>drawer a3</t>
+          <t>Drawer 3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3931,6 +4424,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3946,7 +4441,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>drawer a3</t>
+          <t>Drawer 3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3964,6 +4459,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3979,7 +4476,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>drawer a3</t>
+          <t>Drawer 3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3997,6 +4494,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4012,7 +4511,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>drawer a3</t>
+          <t>Drawer 3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4030,6 +4529,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4045,7 +4546,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>drawer a3</t>
+          <t>Drawer 3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4063,6 +4564,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4078,7 +4581,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>drawer a3</t>
+          <t>Drawer 3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4096,6 +4599,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4111,7 +4616,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4129,6 +4634,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4144,7 +4651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>drawer a3</t>
+          <t>Drawer 3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4162,6 +4669,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4177,7 +4686,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>drawer a3</t>
+          <t>Drawer 3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4195,6 +4704,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4210,7 +4721,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>drawer a4</t>
+          <t>Drawer 4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4228,6 +4739,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4243,7 +4756,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>drawer a4</t>
+          <t>Drawer 4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4261,6 +4774,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4276,7 +4791,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>drawer a4</t>
+          <t>Drawer 4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4294,6 +4809,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4309,7 +4826,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>drawer a4</t>
+          <t>Drawer 4</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4327,6 +4844,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4356,6 +4875,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4371,7 +4892,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>drawer a4</t>
+          <t>Drawer 4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4389,6 +4910,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4404,7 +4927,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>drawer c4</t>
+          <t>Drawer 22</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4422,6 +4945,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4437,7 +4962,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>drawer a4</t>
+          <t>Drawer 4</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4455,6 +4980,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4470,7 +4997,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>drawer a4</t>
+          <t>Drawer 4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4488,6 +5015,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4503,7 +5032,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>drawer a4</t>
+          <t>Drawer 4</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4521,6 +5050,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4536,7 +5067,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>drawer a4</t>
+          <t>Drawer 4</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4554,6 +5085,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4569,7 +5102,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4587,6 +5120,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4602,7 +5137,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4620,6 +5155,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4635,7 +5172,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>drawer a4</t>
+          <t>Drawer 4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4653,6 +5190,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4668,7 +5207,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>drawer a4</t>
+          <t>Drawer 4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4686,6 +5225,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4701,7 +5242,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>drawer a5</t>
+          <t>Drawer 5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4719,6 +5260,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4734,7 +5277,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>drawer b8</t>
+          <t>Drawer 17</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4752,6 +5295,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4781,6 +5326,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4796,7 +5343,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>drawer a5</t>
+          <t>Drawer 5</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4814,6 +5361,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4829,7 +5378,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>drawer a5</t>
+          <t>Drawer 5</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4847,6 +5396,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4862,7 +5413,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>drawer a5</t>
+          <t>Drawer 5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4880,6 +5431,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4895,7 +5448,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>drawer a5</t>
+          <t>Drawer 5</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4913,6 +5466,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4928,7 +5483,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>drawer a5</t>
+          <t>Drawer 5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4946,6 +5501,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4961,7 +5518,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>drawer a6</t>
+          <t>Drawer 6</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4979,6 +5536,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4994,7 +5553,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>drawer a6</t>
+          <t>Drawer 6</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5012,6 +5571,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5027,7 +5588,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>drawer a6</t>
+          <t>Drawer 6</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5045,6 +5606,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5060,7 +5623,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>drawer a6</t>
+          <t>Drawer 6</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5078,6 +5641,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5093,7 +5658,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>drawer a6</t>
+          <t>Drawer 6</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5111,6 +5676,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5126,7 +5693,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>drawer a6</t>
+          <t>Drawer 6</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5144,6 +5711,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5159,7 +5728,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>drawer a6</t>
+          <t>Drawer 6</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5177,6 +5746,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5192,7 +5763,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>drawer a6</t>
+          <t>Drawer 6</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5210,6 +5781,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5225,7 +5798,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>drawer a6</t>
+          <t>Drawer 6</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5243,6 +5816,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5258,7 +5833,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>drawer a6</t>
+          <t>Drawer 6</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5276,6 +5851,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5291,7 +5868,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>drawer a6</t>
+          <t>Drawer 6</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5309,6 +5886,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5324,7 +5903,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>drawer a6</t>
+          <t>Drawer 6</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5342,6 +5921,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5357,7 +5938,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>drawer a7</t>
+          <t>Drawer 7</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5375,6 +5956,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5390,7 +5973,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>drawer a8</t>
+          <t>Drawer 8</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5408,6 +5991,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5423,7 +6008,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5441,6 +6026,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5456,7 +6043,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>drawer a8</t>
+          <t>Drawer 8</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5474,6 +6061,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5489,7 +6078,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>drawer a8</t>
+          <t>Drawer 8</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5507,6 +6096,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5522,7 +6113,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>drawer c8</t>
+          <t>Drawer 26</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5540,6 +6131,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5555,7 +6148,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>drawer a8</t>
+          <t>Drawer 8</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5573,6 +6166,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5588,7 +6183,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>drawer a8</t>
+          <t>Drawer 8</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5606,6 +6201,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5621,7 +6218,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>drawer a8</t>
+          <t>Drawer 8</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5639,6 +6236,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5654,7 +6253,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>drawer a8</t>
+          <t>Drawer 8</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5672,6 +6271,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5687,7 +6288,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>drawer a8</t>
+          <t>Drawer 8</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5705,6 +6306,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5720,7 +6323,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5738,6 +6341,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5753,7 +6358,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5771,6 +6376,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5786,7 +6393,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5804,6 +6411,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5819,7 +6428,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5837,6 +6446,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5852,7 +6463,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5870,6 +6481,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5885,7 +6498,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5903,6 +6516,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5918,7 +6533,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5936,6 +6551,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5951,7 +6568,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5969,6 +6586,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5984,7 +6603,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -6002,6 +6621,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6017,7 +6638,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6035,6 +6656,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6050,7 +6673,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -6068,6 +6691,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6083,7 +6708,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -6101,6 +6726,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6116,7 +6743,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6134,6 +6761,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6149,7 +6778,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6167,6 +6796,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6182,7 +6813,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -6200,6 +6831,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6215,7 +6848,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -6233,6 +6866,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6248,7 +6883,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6266,6 +6901,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6281,7 +6918,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>drawer a9</t>
+          <t>Drawer 9</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6299,6 +6936,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6314,7 +6953,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>drawer b3</t>
+          <t>Drawer 12</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6332,6 +6971,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6347,7 +6988,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>drawer b1</t>
+          <t>Drawer 10</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6365,6 +7006,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6380,7 +7023,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>drawer b3</t>
+          <t>Drawer 12</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6398,6 +7041,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6413,7 +7058,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>drawer b1</t>
+          <t>Drawer 10</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6431,6 +7076,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6446,7 +7093,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>drawer b1</t>
+          <t>Drawer 10</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6464,6 +7111,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6479,7 +7128,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>drawer b1</t>
+          <t>Drawer 10</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6497,6 +7146,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6512,7 +7163,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>drawer b2</t>
+          <t>Drawer 11</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6530,6 +7181,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6545,7 +7198,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>drawer b2</t>
+          <t>Drawer 11</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6563,6 +7216,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6578,7 +7233,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>drawer b2</t>
+          <t>Drawer 11</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6596,6 +7251,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6611,7 +7268,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>drawer b2</t>
+          <t>Drawer 11</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6629,6 +7286,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6644,7 +7303,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>drawer b5</t>
+          <t>Drawer 14</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6662,6 +7321,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6691,6 +7352,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6706,7 +7369,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>drawer b2</t>
+          <t>Drawer 11</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6724,6 +7387,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6739,7 +7404,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>drawer b2</t>
+          <t>Drawer 11</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6757,6 +7422,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6772,7 +7439,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>drawer b2</t>
+          <t>Drawer 11</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6790,6 +7457,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6805,7 +7474,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>drawer b2</t>
+          <t>Drawer 11</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6823,6 +7492,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6838,7 +7509,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>drawer b3</t>
+          <t>Drawer 12</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6856,6 +7527,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6871,7 +7544,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>drawer b3</t>
+          <t>Drawer 12</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6889,6 +7562,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6904,7 +7579,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>drawer b3</t>
+          <t>Drawer 12</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6922,6 +7597,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6937,7 +7614,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6955,6 +7632,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -6970,7 +7649,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6988,6 +7667,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7003,7 +7684,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>drawer b3</t>
+          <t>Drawer 12</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7021,6 +7702,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7036,7 +7719,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>drawer b3</t>
+          <t>Drawer 12</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7054,6 +7737,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7069,7 +7754,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>drawer b3</t>
+          <t>Drawer 12</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7087,6 +7772,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7102,7 +7789,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>drawer b3</t>
+          <t>Drawer 12</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7120,6 +7807,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7135,7 +7824,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>drawer b3</t>
+          <t>Drawer 12</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7153,6 +7842,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7168,7 +7859,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>drawer c8</t>
+          <t>Drawer 26</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7186,6 +7877,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7201,7 +7894,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>drawer b3</t>
+          <t>Drawer 12</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7219,6 +7912,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7234,7 +7929,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>drawer b3</t>
+          <t>Drawer 12</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7252,6 +7947,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7267,7 +7964,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>drawer b3</t>
+          <t>Drawer 12</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7285,6 +7982,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7300,7 +7999,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>drawer b4</t>
+          <t>Drawer 13</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -7318,6 +8017,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7333,7 +8034,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>drawer b4</t>
+          <t>Drawer 13</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -7351,6 +8052,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7366,7 +8069,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>drawer b4</t>
+          <t>Drawer 13</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7384,6 +8087,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -7399,7 +8104,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>drawer b4</t>
+          <t>Drawer 13</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7417,6 +8122,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7432,7 +8139,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>drawer b4</t>
+          <t>Drawer 13</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -7450,6 +8157,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7465,7 +8174,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>drawer b4</t>
+          <t>Drawer 13</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7483,6 +8192,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7498,7 +8209,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>drawer b4</t>
+          <t>Drawer 13</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7516,6 +8227,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -7531,7 +8244,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>drawer b5</t>
+          <t>Drawer 14</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -7549,6 +8262,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7564,7 +8279,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>drawer b5</t>
+          <t>Drawer 14</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -7582,6 +8297,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -7597,7 +8314,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>drawer b5</t>
+          <t>Drawer 14</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7615,6 +8332,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -7630,7 +8349,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>drawer b5</t>
+          <t>Drawer 14</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7648,6 +8367,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -7663,7 +8384,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>drawer b5</t>
+          <t>Drawer 14</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -7681,6 +8402,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -7696,7 +8419,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>drawer b5</t>
+          <t>Drawer 14</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -7714,6 +8437,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -7729,7 +8454,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>drawer b5</t>
+          <t>Drawer 14</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -7747,6 +8472,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -7762,7 +8489,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>drawer b5</t>
+          <t>Drawer 14</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -7780,6 +8507,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -7809,6 +8538,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -7824,7 +8555,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>drawer b5</t>
+          <t>Drawer 14</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -7842,6 +8573,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -7857,7 +8590,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>drawer b6</t>
+          <t>Drawer 15</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -7875,6 +8608,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -7904,6 +8639,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -7919,7 +8656,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>drawer b6</t>
+          <t>Drawer 15</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7937,6 +8674,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -7952,7 +8691,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>drawer b6</t>
+          <t>Drawer 15</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -7970,6 +8709,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -7985,7 +8726,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>drawer b6</t>
+          <t>Drawer 15</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8003,6 +8744,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8018,7 +8761,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>drawer b7</t>
+          <t>Drawer 16</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8036,6 +8779,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8051,7 +8796,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>drawer b7</t>
+          <t>Drawer 16</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8069,6 +8814,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -8084,7 +8831,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>drawer b8</t>
+          <t>Drawer 17</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8102,6 +8849,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8117,7 +8866,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>drawer b8</t>
+          <t>Drawer 17</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8135,6 +8884,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -8164,6 +8915,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -8179,7 +8932,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>drawer b8</t>
+          <t>Drawer 17</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -8197,6 +8950,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -8212,7 +8967,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>drawer b8</t>
+          <t>Drawer 17</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -8230,6 +8985,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -8245,7 +9002,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>drawer b8</t>
+          <t>Drawer 17</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -8263,6 +9020,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -8278,7 +9037,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>drawer b8</t>
+          <t>Drawer 17</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -8296,6 +9055,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -8311,7 +9072,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>drawer b9</t>
+          <t>Drawer 18</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -8329,6 +9090,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -8344,7 +9107,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>drawer b9</t>
+          <t>Drawer 18</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -8362,6 +9125,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -8377,7 +9142,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -8395,6 +9160,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -8410,7 +9177,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -8428,6 +9195,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -8443,7 +9212,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -8461,6 +9230,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -8476,7 +9247,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -8494,6 +9265,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -8509,7 +9282,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -8527,6 +9300,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -8542,7 +9317,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -8560,6 +9335,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -8575,7 +9352,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8593,6 +9370,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -8608,7 +9387,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8626,6 +9405,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -8641,7 +9422,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8659,6 +9440,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -8674,7 +9457,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -8692,6 +9475,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -8707,7 +9492,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -8725,6 +9510,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -8740,7 +9527,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>drawer c1</t>
+          <t>Drawer 19</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -8758,6 +9545,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -8773,7 +9562,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8791,6 +9580,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -8806,7 +9597,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -8824,6 +9615,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -8839,7 +9632,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -8857,6 +9650,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -8872,7 +9667,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -8890,6 +9685,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -8905,7 +9702,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -8923,6 +9720,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -8938,7 +9737,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8956,6 +9755,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -8971,7 +9772,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -8989,6 +9790,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -9004,7 +9807,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -9022,6 +9825,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -9037,7 +9842,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -9055,6 +9860,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -9070,7 +9877,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -9088,6 +9895,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -9103,7 +9912,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -9121,6 +9930,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -9150,6 +9961,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -9165,7 +9978,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -9183,6 +9996,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -9198,7 +10013,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -9216,6 +10031,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -9231,7 +10048,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -9247,6 +10064,11 @@
       <c r="G183" s="2" t="inlineStr">
         <is>
           <t>Google it</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>udoo quad core ddr3 1gb 4 port imx6quad</t>
         </is>
       </c>
     </row>
@@ -9264,7 +10086,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>drawer c3</t>
+          <t>Drawer 21</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -9282,6 +10104,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -9297,7 +10121,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>drawer c4</t>
+          <t>Drawer 22</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -9315,6 +10139,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -9330,7 +10156,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>drawer c5</t>
+          <t>Drawer 23</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -9348,6 +10174,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -9363,7 +10191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>drawer c5</t>
+          <t>Drawer 23</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -9381,6 +10209,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -9396,7 +10226,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>drawer c5</t>
+          <t>Drawer 23</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -9414,6 +10244,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -9429,7 +10261,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>drawer c7</t>
+          <t>Drawer 25</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -9447,6 +10279,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -9462,7 +10296,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>drawer c8</t>
+          <t>Drawer 26</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -9480,6 +10314,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -9509,6 +10345,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -9524,7 +10362,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>drawer c8</t>
+          <t>Drawer 26</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -9542,6 +10380,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -9557,7 +10397,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>drawer c8</t>
+          <t>Drawer 26</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -9575,6 +10415,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -9590,7 +10432,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>drawer c8</t>
+          <t>Drawer 26</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -9608,6 +10450,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -9623,7 +10467,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>drawer c8</t>
+          <t>Drawer 26</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -9641,6 +10485,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -9656,7 +10502,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>drawer c9</t>
+          <t>Drawer 27</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -9674,6 +10520,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -9689,7 +10537,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>drawer c9</t>
+          <t>Drawer 27</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -9707,6 +10555,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -9722,7 +10572,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>drawer c9</t>
+          <t>Drawer 27</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -9740,6 +10590,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -9769,6 +10621,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -9798,6 +10652,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -9827,6 +10683,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -9856,6 +10714,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -9885,6 +10745,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -9914,6 +10776,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -9943,6 +10807,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -9972,6 +10838,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -10001,6 +10869,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -10030,6 +10900,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -10059,6 +10931,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -10088,6 +10962,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -10117,6 +10993,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -10146,6 +11024,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -10175,6 +11055,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -10204,6 +11086,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -10233,6 +11117,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -10262,6 +11148,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -10291,6 +11179,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -10320,6 +11210,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -10349,6 +11241,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -10378,6 +11272,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -10407,6 +11303,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -10436,6 +11334,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -10465,6 +11365,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -10494,6 +11396,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -10523,6 +11427,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -10552,6 +11458,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -10581,6 +11489,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -10610,6 +11520,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -10639,6 +11551,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -10668,6 +11582,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -10697,6 +11613,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -10726,6 +11644,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -10755,6 +11675,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -10784,6 +11706,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -10813,6 +11737,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -10842,6 +11768,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -10871,6 +11799,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -10900,6 +11830,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -10929,6 +11861,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -10958,6 +11892,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -10987,6 +11923,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -11016,6 +11954,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -11045,6 +11985,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -11074,6 +12016,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -11103,6 +12047,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -11132,6 +12078,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -11161,6 +12109,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -11190,6 +12140,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -11219,6 +12171,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -11248,6 +12202,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -11277,6 +12233,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -11306,6 +12264,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -11335,6 +12295,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -11364,6 +12326,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -11393,6 +12357,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -11422,6 +12388,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -11451,6 +12419,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -11480,6 +12450,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -11509,6 +12481,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -11538,6 +12512,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -11567,6 +12543,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -11596,6 +12574,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -11625,6 +12605,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -11654,6 +12636,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -11683,6 +12667,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -11712,6 +12698,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -11741,6 +12729,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -11770,6 +12760,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -11799,6 +12791,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -11828,6 +12822,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -11857,6 +12853,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -11886,6 +12884,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -11915,6 +12915,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -11944,6 +12946,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -11973,6 +12977,8 @@
           <t>Google it</t>
         </is>
       </c>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I275"/>
